--- a/neuroimaging conversion structural/Example data NIfTI/reference_data/pdf_pet/sub-0009_ses-01_pet_pdf.xlsx
+++ b/neuroimaging conversion structural/Example data NIfTI/reference_data/pdf_pet/sub-0009_ses-01_pet_pdf.xlsx
@@ -1,6 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <fileVersion appName="libxl" rupBuild="4.6.0"/>
   <workbookPr/>
   <bookViews>
     <workbookView activeTab="0"/>
@@ -450,7 +451,7 @@
         <v>0.05052418845522294</v>
       </c>
       <c r="CM1" s="0">
-        <v>0.018632383081796162</v>
+        <v>0.018632383081796163</v>
       </c>
       <c r="CN1" s="0">
         <v>0.023929169657812877</v>
@@ -605,7 +606,7 @@
         <v>0</v>
       </c>
       <c r="V2" s="0">
-        <v>0.030637254901960786</v>
+        <v>0.030637254901960787</v>
       </c>
       <c r="W2" s="0">
         <v>0.034188034188034191</v>
@@ -752,7 +753,7 @@
         <v>0</v>
       </c>
       <c r="BS2" s="0">
-        <v>0.096934448079486243</v>
+        <v>0.096934448079486244</v>
       </c>
       <c r="BT2" s="0">
         <v>0.063597049096921904</v>
@@ -1174,7 +1175,7 @@
         <v>0.031577617784514338</v>
       </c>
       <c r="CM3" s="0">
-        <v>0.018632383081796162</v>
+        <v>0.018632383081796163</v>
       </c>
       <c r="CN3" s="0">
         <v>0</v>
@@ -1416,7 +1417,7 @@
         <v>0.081029069178567809</v>
       </c>
       <c r="AY4" s="0">
-        <v>0.020222446916076844</v>
+        <v>0.020222446916076845</v>
       </c>
       <c r="AZ4" s="0">
         <v>0.0061751265900950973</v>
@@ -1793,7 +1794,7 @@
         <v>0.076180802437785675</v>
       </c>
       <c r="BD5" s="0">
-        <v>0.068516615279205217</v>
+        <v>0.068516615279205218</v>
       </c>
       <c r="BE5" s="0">
         <v>0.093764650726676044</v>
@@ -2448,7 +2449,7 @@
         <v>0</v>
       </c>
       <c r="AG7" s="0">
-        <v>0.037724460540214277</v>
+        <v>0.037724460540214278</v>
       </c>
       <c r="AH7" s="0">
         <v>0</v>
@@ -2858,7 +2859,7 @@
         <v>0.052164840897235269</v>
       </c>
       <c r="AW8" s="0">
-        <v>0.062791532113383577</v>
+        <v>0.062791532113383578</v>
       </c>
       <c r="AX8" s="0">
         <v>0.14180087106249367</v>
@@ -2882,7 +2883,7 @@
         <v>0.075368276807125725</v>
       </c>
       <c r="BE8" s="0">
-        <v>0.062509767151117362</v>
+        <v>0.062509767151117363</v>
       </c>
       <c r="BF8" s="0">
         <v>0</v>
@@ -3286,7 +3287,7 @@
         <v>0.016145959473641707</v>
       </c>
       <c r="BS9" s="0">
-        <v>0.29080334423845849</v>
+        <v>0.2908033442384585</v>
       </c>
       <c r="BT9" s="0">
         <v>0.30526583566522486</v>
@@ -3307,7 +3308,7 @@
         <v>0</v>
       </c>
       <c r="BZ9" s="0">
-        <v>0.026329647182727726</v>
+        <v>0.026329647182727727</v>
       </c>
       <c r="CA9" s="0">
         <v>0</v>
@@ -3525,10 +3526,10 @@
         <v>0.16548463356974011</v>
       </c>
       <c r="AD10" s="0">
-        <v>0.095170116583392902</v>
+        <v>0.095170116583392903</v>
       </c>
       <c r="AE10" s="0">
-        <v>0.068306010928961824</v>
+        <v>0.068306010928961825</v>
       </c>
       <c r="AF10" s="0">
         <v>0</v>
@@ -3588,7 +3589,7 @@
         <v>0.30385900941962957</v>
       </c>
       <c r="AY10" s="0">
-        <v>0.067408156386922879</v>
+        <v>0.06740815638692288</v>
       </c>
       <c r="AZ10" s="0">
         <v>0.055576139310855928</v>
@@ -3654,7 +3655,7 @@
         <v>0.34766386839650676</v>
       </c>
       <c r="BU10" s="0">
-        <v>0.08289296445964156</v>
+        <v>0.082892964459641561</v>
       </c>
       <c r="BV10" s="0">
         <v>0.016380016380016394</v>
@@ -3863,7 +3864,7 @@
         <v>0.13013571295779874</v>
       </c>
       <c r="V11" s="0">
-        <v>0.29105392156862719</v>
+        <v>0.2910539215686272</v>
       </c>
       <c r="W11" s="0">
         <v>0.22222222222222204</v>
@@ -4037,7 +4038,7 @@
         <v>0</v>
       </c>
       <c r="CB11" s="0">
-        <v>0.052493438320209924</v>
+        <v>0.052493438320209925</v>
       </c>
       <c r="CC11" s="0">
         <v>0.22497187851518541</v>
@@ -4342,16 +4343,16 @@
         <v>0.22869254796965663</v>
       </c>
       <c r="BI12" s="0">
-        <v>0.075309306078536919</v>
+        <v>0.07530930607853692</v>
       </c>
       <c r="BJ12" s="0">
-        <v>0.12898470609913409</v>
+        <v>0.1289847060991341</v>
       </c>
       <c r="BK12" s="0">
-        <v>0.42585342399890141</v>
+        <v>0.42585342399890142</v>
       </c>
       <c r="BL12" s="0">
-        <v>0.0063686154629983499</v>
+        <v>0.00636861546299835</v>
       </c>
       <c r="BM12" s="0">
         <v>0.52146706066400184</v>
@@ -4560,7 +4561,7 @@
         <v>0</v>
       </c>
       <c r="M13" s="0">
-        <v>0.027720027720027698</v>
+        <v>0.027720027720027699</v>
       </c>
       <c r="N13" s="0">
         <v>0</v>
@@ -4602,7 +4603,7 @@
         <v>0</v>
       </c>
       <c r="AA13" s="0">
-        <v>0.23453532688361164</v>
+        <v>0.23453532688361165</v>
       </c>
       <c r="AB13" s="0">
         <v>0.16349887594522772</v>
@@ -4662,7 +4663,7 @@
         <v>0.11129660545353358</v>
       </c>
       <c r="AU13" s="0">
-        <v>0.037091988130563767</v>
+        <v>0.037091988130563768</v>
       </c>
       <c r="AV13" s="0">
         <v>0.11923392205082337</v>
@@ -4686,7 +4687,7 @@
         <v>0.039424403705893916</v>
       </c>
       <c r="BC13" s="0">
-        <v>0.37243947858472964</v>
+        <v>0.37243947858472965</v>
       </c>
       <c r="BD13" s="0">
         <v>0.26036313806097955</v>
@@ -5009,7 +5010,7 @@
         <v>0.22471910112359572</v>
       </c>
       <c r="AP14" s="0">
-        <v>0.32376747608535716</v>
+        <v>0.32376747608535717</v>
       </c>
       <c r="AQ14" s="0">
         <v>0.24320457796852671</v>
@@ -5114,7 +5115,7 @@
         <v>0.014023278642546641</v>
       </c>
       <c r="BY14" s="0">
-        <v>0.069676700111482789</v>
+        <v>0.06967670011148279</v>
       </c>
       <c r="BZ14" s="0">
         <v>0.026329647182727775</v>
@@ -5284,7 +5285,7 @@
         <v>0.017758835020422643</v>
       </c>
       <c r="M15" s="0">
-        <v>0.027720027720027698</v>
+        <v>0.027720027720027699</v>
       </c>
       <c r="N15" s="0">
         <v>0</v>
@@ -5485,7 +5486,7 @@
         <v>0</v>
       </c>
       <c r="CB15" s="0">
-        <v>0.052493438320209924</v>
+        <v>0.052493438320209925</v>
       </c>
       <c r="CC15" s="0">
         <v>0.38745156855393043</v>
@@ -5700,10 +5701,10 @@
         <v>0.68998334522959859</v>
       </c>
       <c r="AE16" s="0">
-        <v>0.068306010928961824</v>
+        <v>0.068306010928961825</v>
       </c>
       <c r="AF16" s="0">
-        <v>0.28070175438596517</v>
+        <v>0.28070175438596518</v>
       </c>
       <c r="AG16" s="0">
         <v>0.21880187113324301</v>
@@ -5739,7 +5740,7 @@
         <v>0.34334763948497887</v>
       </c>
       <c r="AR16" s="0">
-        <v>0.087227414330218161</v>
+        <v>0.087227414330218162</v>
       </c>
       <c r="AS16" s="0">
         <v>0.066137566137566203</v>
@@ -5793,7 +5794,7 @@
         <v>0.2151694459386769</v>
       </c>
       <c r="BJ16" s="0">
-        <v>0.3316749585406305</v>
+        <v>0.33167495854063051</v>
       </c>
       <c r="BK16" s="0">
         <v>0.79675801909471877</v>
@@ -5883,7 +5884,7 @@
         <v>0.16769144773616562</v>
       </c>
       <c r="CN16" s="0">
-        <v>0.32304379038047409</v>
+        <v>0.3230437903804741</v>
       </c>
       <c r="CO16" s="0">
         <v>0.36145640483117381</v>
@@ -6053,7 +6054,7 @@
         <v>0.29316915860451459</v>
       </c>
       <c r="AB17" s="0">
-        <v>0.20437359493153467</v>
+        <v>0.20437359493153468</v>
       </c>
       <c r="AC17" s="0">
         <v>0.42553191489361664</v>
@@ -6140,7 +6141,7 @@
         <v>0.58924289140116426</v>
       </c>
       <c r="BE17" s="0">
-        <v>0.82825441475230432</v>
+        <v>0.82825441475230433</v>
       </c>
       <c r="BF17" s="0">
         <v>0.069415521310564984</v>
@@ -6155,7 +6156,7 @@
         <v>0.25103102026178925</v>
       </c>
       <c r="BJ17" s="0">
-        <v>0.39432467293163775</v>
+        <v>0.39432467293163776</v>
       </c>
       <c r="BK17" s="0">
         <v>0.73494058657874795</v>
@@ -6373,7 +6374,7 @@
         <v>0.055440055440055397</v>
       </c>
       <c r="N18" s="0">
-        <v>0.041536863966770476</v>
+        <v>0.041536863966770477</v>
       </c>
       <c r="O18" s="0">
         <v>0.07909827961241836</v>
@@ -6415,7 +6416,7 @@
         <v>0.55702140134857758</v>
       </c>
       <c r="AB18" s="0">
-        <v>0.20437359493153467</v>
+        <v>0.20437359493153468</v>
       </c>
       <c r="AC18" s="0">
         <v>0.47281323877068515</v>
@@ -6538,7 +6539,7 @@
         <v>0.36743092298647817</v>
       </c>
       <c r="BQ18" s="0">
-        <v>0.40679588418281853</v>
+        <v>0.40679588418281854</v>
       </c>
       <c r="BR18" s="0">
         <v>0.14531363526277535</v>
@@ -6586,7 +6587,7 @@
         <v>0</v>
       </c>
       <c r="CG18" s="0">
-        <v>0.13000059091177676</v>
+        <v>0.13000059091177677</v>
       </c>
       <c r="CH18" s="0">
         <v>0.15017004549269011</v>
@@ -6765,7 +6766,7 @@
         <v>0.76923076923077138</v>
       </c>
       <c r="X19" s="0">
-        <v>0.24635209399279961</v>
+        <v>0.24635209399279962</v>
       </c>
       <c r="Y19" s="0">
         <v>0.70754716981132271</v>
@@ -6840,7 +6841,7 @@
         <v>0.35024964602429487</v>
       </c>
       <c r="AW19" s="0">
-        <v>0.53821313240043211</v>
+        <v>0.53821313240043212</v>
       </c>
       <c r="AX19" s="0">
         <v>0.85080522637496447</v>
@@ -6873,7 +6874,7 @@
         <v>0.067775723967960749</v>
       </c>
       <c r="BH19" s="0">
-        <v>0.73070058009817251</v>
+        <v>0.73070058009817252</v>
       </c>
       <c r="BI19" s="0">
         <v>0.38013268782499654</v>
@@ -6912,7 +6913,7 @@
         <v>1.1235478673789567</v>
       </c>
       <c r="BU19" s="0">
-        <v>0.41446482229820863</v>
+        <v>0.41446482229820864</v>
       </c>
       <c r="BV19" s="0">
         <v>0.11466011466011498</v>
@@ -6954,7 +6955,7 @@
         <v>0.23408860032684134</v>
       </c>
       <c r="CI19" s="0">
-        <v>0.066555740432612503</v>
+        <v>0.066555740432612504</v>
       </c>
       <c r="CJ19" s="0">
         <v>0.010541851149061806</v>
@@ -7142,7 +7143,7 @@
         <v>0.3883098303699159</v>
       </c>
       <c r="AC20" s="0">
-        <v>0.59101654846335649</v>
+        <v>0.5910165484633565</v>
       </c>
       <c r="AD20" s="0">
         <v>0.90411610754223093</v>
@@ -7226,7 +7227,7 @@
         <v>0.77423775265501815</v>
       </c>
       <c r="BE20" s="0">
-        <v>0.82825441475230432</v>
+        <v>0.82825441475230433</v>
       </c>
       <c r="BF20" s="0">
         <v>0.23601277245592092</v>
@@ -7522,7 +7523,7 @@
         <v>0.087218522042499136</v>
       </c>
       <c r="AI21" s="0">
-        <v>0.34458295327860516</v>
+        <v>0.34458295327860517</v>
       </c>
       <c r="AJ21" s="0">
         <v>0.79463364293085581</v>
@@ -7531,7 +7532,7 @@
         <v>0.27486813758264594</v>
       </c>
       <c r="AL21" s="0">
-        <v>0.22570452053911116</v>
+        <v>0.22570452053911117</v>
       </c>
       <c r="AM21" s="0">
         <v>0.6178560395427859</v>
@@ -7555,7 +7556,7 @@
         <v>0.066137566137566078</v>
       </c>
       <c r="AT21" s="0">
-        <v>0.44518642181413431</v>
+        <v>0.44518642181413432</v>
       </c>
       <c r="AU21" s="0">
         <v>0.3771018793273983</v>
@@ -7579,7 +7580,7 @@
         <v>1.2792282688476448</v>
       </c>
       <c r="BB21" s="0">
-        <v>0.23654642223536348</v>
+        <v>0.23654642223536349</v>
       </c>
       <c r="BC21" s="0">
         <v>0.91840189605552647</v>
@@ -7633,7 +7634,7 @@
         <v>1.1914859243103508</v>
       </c>
       <c r="BT21" s="0">
-        <v>1.0769100313745434</v>
+        <v>1.0769100313745435</v>
       </c>
       <c r="BU21" s="0">
         <v>0.62169723344731054</v>
@@ -7803,7 +7804,7 @@
         <v>0.053418803418803368</v>
       </c>
       <c r="H22" s="0">
-        <v>0.050459178524573572</v>
+        <v>0.050459178524573573</v>
       </c>
       <c r="I22" s="0">
         <v>0.04983388704318932</v>
@@ -7980,7 +7981,7 @@
         <v>0.20697505950532943</v>
       </c>
       <c r="BO22" s="0">
-        <v>0.66419002589215292</v>
+        <v>0.66419002589215293</v>
       </c>
       <c r="BP22" s="0">
         <v>0.7054673721340381</v>
@@ -8010,7 +8011,7 @@
         <v>0.33655868742111872</v>
       </c>
       <c r="BY22" s="0">
-        <v>0.34838350055741329</v>
+        <v>0.3483835005574133</v>
       </c>
       <c r="BZ22" s="0">
         <v>0.21063717746182181</v>
@@ -8040,7 +8041,7 @@
         <v>0.37100834768782265</v>
       </c>
       <c r="CI22" s="0">
-        <v>0.26622296173044901</v>
+        <v>0.26622296173044902</v>
       </c>
       <c r="CJ22" s="0">
         <v>0.063251106894370593</v>
@@ -8168,10 +8169,10 @@
         <v>0.080734685639318016</v>
       </c>
       <c r="I23" s="0">
-        <v>0.088593576965670245</v>
+        <v>0.088593576965670246</v>
       </c>
       <c r="J23" s="0">
-        <v>0.095914061001343059</v>
+        <v>0.09591406100134306</v>
       </c>
       <c r="K23" s="0">
         <v>0.038008361839604821</v>
@@ -8195,7 +8196,7 @@
         <v>0.051440329218107136</v>
       </c>
       <c r="R23" s="0">
-        <v>0.045913682277318769</v>
+        <v>0.04591368227731877</v>
       </c>
       <c r="S23" s="0">
         <v>0.17182130584192487</v>
@@ -8222,10 +8223,10 @@
         <v>0.22878059940517109</v>
       </c>
       <c r="AA23" s="0">
-        <v>0.76223981237174065</v>
+        <v>0.76223981237174066</v>
       </c>
       <c r="AB23" s="0">
-        <v>0.49049662783568498</v>
+        <v>0.49049662783568499</v>
       </c>
       <c r="AC23" s="0">
         <v>1.0401891252955111</v>
@@ -8249,7 +8250,7 @@
         <v>0.50673963717442128</v>
       </c>
       <c r="AJ23" s="0">
-        <v>0.89783281733746378</v>
+        <v>0.89783281733746379</v>
       </c>
       <c r="AK23" s="0">
         <v>0.31944134908253563</v>
@@ -8279,7 +8280,7 @@
         <v>0.5952380952380969</v>
       </c>
       <c r="AT23" s="0">
-        <v>0.7234279354479709</v>
+        <v>0.72342793544797091</v>
       </c>
       <c r="AU23" s="0">
         <v>0.46983184965380942</v>
@@ -8321,13 +8322,13 @@
         <v>0.16019716574245271</v>
       </c>
       <c r="BH23" s="0">
-        <v>0.95939312806782961</v>
+        <v>0.95939312806782962</v>
       </c>
       <c r="BI23" s="0">
         <v>0.68854222700376733</v>
       </c>
       <c r="BJ23" s="0">
-        <v>0.79970517781463279</v>
+        <v>0.7997051778146328</v>
       </c>
       <c r="BK23" s="0">
         <v>1.270691668383821</v>
@@ -8489,7 +8490,7 @@
         <v>0.36985668053629323</v>
       </c>
       <c r="DL23" s="0">
-        <v>0.17406440382941737</v>
+        <v>0.17406440382941738</v>
       </c>
       <c r="DM23" s="0">
         <v>0</v>
@@ -8536,7 +8537,7 @@
         <v>0.089519790267919855</v>
       </c>
       <c r="K24" s="0">
-        <v>0.17103762827822105</v>
+        <v>0.17103762827822106</v>
       </c>
       <c r="L24" s="0">
         <v>0.10655301012253586</v>
@@ -8641,7 +8642,7 @@
         <v>0.19841269841269824</v>
       </c>
       <c r="AT24" s="0">
-        <v>0.44518642181413431</v>
+        <v>0.44518642181413432</v>
       </c>
       <c r="AU24" s="0">
         <v>0.46364985163204708</v>
@@ -8668,7 +8669,7 @@
         <v>0.29568302779420436</v>
       </c>
       <c r="BC24" s="0">
-        <v>1.0707635009310978</v>
+        <v>1.0707635009310979</v>
       </c>
       <c r="BD24" s="0">
         <v>1.0071942446043156</v>
@@ -8761,13 +8762,13 @@
         <v>0.3840926549666131</v>
       </c>
       <c r="CH24" s="0">
-        <v>0.47701073274148625</v>
+        <v>0.47701073274148626</v>
       </c>
       <c r="CI24" s="0">
         <v>0.19966722129783676</v>
       </c>
       <c r="CJ24" s="0">
-        <v>0.084334809192494128</v>
+        <v>0.084334809192494129</v>
       </c>
       <c r="CK24" s="0">
         <v>0.52504611891585029</v>
@@ -8868,13 +8869,13 @@
     </row>
     <row r="25">
       <c r="A25" s="0">
-        <v>0.18113754377490623</v>
+        <v>0.18113754377490624</v>
       </c>
       <c r="B25" s="0">
         <v>0.17143335005853805</v>
       </c>
       <c r="C25" s="0">
-        <v>0.23272941523051976</v>
+        <v>0.23272941523051977</v>
       </c>
       <c r="D25" s="0">
         <v>0.15026090757588162</v>
@@ -8883,7 +8884,7 @@
         <v>0.1308288944958414</v>
       </c>
       <c r="F25" s="0">
-        <v>0.16068405497690152</v>
+        <v>0.16068405497690153</v>
       </c>
       <c r="G25" s="0">
         <v>0.093482905982905901</v>
@@ -9015,7 +9016,7 @@
         <v>0.9598134194474337</v>
       </c>
       <c r="AX25" s="0">
-        <v>1.2255646713258372</v>
+        <v>1.2255646713258373</v>
       </c>
       <c r="AY25" s="0">
         <v>0.81563869228176533</v>
@@ -9156,10 +9157,10 @@
         <v>0.015979546180888447</v>
       </c>
       <c r="CS25" s="0">
-        <v>0.04422821760283057</v>
+        <v>0.044228217602830571</v>
       </c>
       <c r="CT25" s="0">
-        <v>0.066746762782005017</v>
+        <v>0.066746762782005018</v>
       </c>
       <c r="CU25" s="0">
         <v>0</v>
@@ -9201,7 +9202,7 @@
         <v>0</v>
       </c>
       <c r="DH25" s="0">
-        <v>0.89126559714794928</v>
+        <v>0.89126559714794929</v>
       </c>
       <c r="DI25" s="0">
         <v>0</v>
@@ -9233,7 +9234,7 @@
         <v>0.19321338002656668</v>
       </c>
       <c r="B26" s="0">
-        <v>0.20906506104699762</v>
+        <v>0.20906506104699763</v>
       </c>
       <c r="C26" s="0">
         <v>0.25335100898512275</v>
@@ -9392,7 +9393,7 @@
         <v>0.66035876207372302</v>
       </c>
       <c r="BC26" s="0">
-        <v>1.2696800406297601</v>
+        <v>1.2696800406297602</v>
       </c>
       <c r="BD26" s="0">
         <v>1.2538540596094541</v>
@@ -9410,10 +9411,10 @@
         <v>1.1546184738955814</v>
       </c>
       <c r="BI26" s="0">
-        <v>0.96109019185942179</v>
+        <v>0.9610901918594218</v>
       </c>
       <c r="BJ26" s="0">
-        <v>1.0466187580615431</v>
+        <v>1.0466187580615432</v>
       </c>
       <c r="BK26" s="0">
         <v>1.3050346864482438</v>
@@ -9527,7 +9528,7 @@
         <v>0.099800399201596723</v>
       </c>
       <c r="CV26" s="0">
-        <v>0.87064676616915337</v>
+        <v>0.87064676616915338</v>
       </c>
       <c r="CW26" s="0">
         <v>0.24268899405411942</v>
@@ -9563,7 +9564,7 @@
         <v>0.10162601626016252</v>
       </c>
       <c r="DH26" s="0">
-        <v>1.158645276292334</v>
+        <v>1.1586452762923341</v>
       </c>
       <c r="DI26" s="0">
         <v>0.31152647975077852</v>
@@ -9646,7 +9647,7 @@
         <v>0.22956841138659301</v>
       </c>
       <c r="S27" s="0">
-        <v>0.36221788799108356</v>
+        <v>0.36221788799108357</v>
       </c>
       <c r="T27" s="0">
         <v>0.1502424366591544</v>
@@ -9733,7 +9734,7 @@
         <v>0.64910979228486587</v>
       </c>
       <c r="AV27" s="0">
-        <v>0.96877561666293976</v>
+        <v>0.96877561666293977</v>
       </c>
       <c r="AW27" s="0">
         <v>1.2289199856476489</v>
@@ -9916,7 +9917,7 @@
         <v>0.71038251366120153</v>
       </c>
       <c r="DE27" s="0">
-        <v>0.096665055582406872</v>
+        <v>0.096665055582406873</v>
       </c>
       <c r="DF27" s="0">
         <v>0.13633265167007488</v>
@@ -9954,7 +9955,7 @@
     </row>
     <row r="28">
       <c r="A28" s="0">
-        <v>0.26164311878597662</v>
+        <v>0.26164311878597663</v>
       </c>
       <c r="B28" s="0">
         <v>0.29687238668673777</v>
@@ -9984,7 +9985,7 @@
         <v>0.28134791227060635</v>
       </c>
       <c r="K28" s="0">
-        <v>0.30406689471683856</v>
+        <v>0.30406689471683857</v>
       </c>
       <c r="L28" s="0">
         <v>0.2131060202450725</v>
@@ -10077,7 +10078,7 @@
         <v>1.3632958801498165</v>
       </c>
       <c r="AP28" s="0">
-        <v>1.0154525386313495</v>
+        <v>1.0154525386313496</v>
       </c>
       <c r="AQ28" s="0">
         <v>1.1158798283261835</v>
@@ -10155,7 +10156,7 @@
         <v>1.1707756388607484</v>
       </c>
       <c r="BP28" s="0">
-        <v>1.2419165196943009</v>
+        <v>1.241916519694301</v>
       </c>
       <c r="BQ28" s="0">
         <v>1.0768126346015823</v>
@@ -10209,7 +10210,7 @@
         <v>0.70909413224605766</v>
       </c>
       <c r="CH28" s="0">
-        <v>0.68901550284881607</v>
+        <v>0.68901550284881608</v>
       </c>
       <c r="CI28" s="0">
         <v>0.46589018302828755</v>
@@ -10230,7 +10231,7 @@
         <v>1.1366355587461148</v>
       </c>
       <c r="CO28" s="0">
-        <v>1.1945693379176618</v>
+        <v>1.1945693379176619</v>
       </c>
       <c r="CP28" s="0">
         <v>1.187192708957912</v>
@@ -10245,7 +10246,7 @@
         <v>0.30222615361934335</v>
       </c>
       <c r="CT28" s="0">
-        <v>0.54732345481244304</v>
+        <v>0.54732345481244305</v>
       </c>
       <c r="CU28" s="0">
         <v>0.39920159680638839</v>
@@ -10284,7 +10285,7 @@
         <v>0.20449897750511306</v>
       </c>
       <c r="DG28" s="0">
-        <v>0.50813008130081438</v>
+        <v>0.50813008130081439</v>
       </c>
       <c r="DH28" s="0">
         <v>2.2281639928698818</v>
@@ -10305,7 +10306,7 @@
         <v>1.2108262108262142</v>
       </c>
       <c r="DN28" s="0">
-        <v>1.5625000000000044</v>
+        <v>1.5625000000000045</v>
       </c>
       <c r="DO28" s="0">
         <v>0.88996763754045549</v>
@@ -10343,7 +10344,7 @@
         <v>0.26024363233665537</v>
       </c>
       <c r="J29" s="0">
-        <v>0.38365624400537079</v>
+        <v>0.3836562440053708</v>
       </c>
       <c r="K29" s="0">
         <v>0.34207525655644211</v>
@@ -10385,7 +10386,7 @@
         <v>1.076923076923076</v>
       </c>
       <c r="X29" s="0">
-        <v>0.73905628197839623</v>
+        <v>0.73905628197839624</v>
       </c>
       <c r="Y29" s="0">
         <v>1.0744234800838566</v>
@@ -10436,7 +10437,7 @@
         <v>1.8687527162103417</v>
       </c>
       <c r="AO29" s="0">
-        <v>1.3333333333333321</v>
+        <v>1.3333333333333322</v>
       </c>
       <c r="AP29" s="0">
         <v>1.427520235467254</v>
@@ -10472,7 +10473,7 @@
         <v>0.98184512782511957</v>
       </c>
       <c r="BA29" s="0">
-        <v>1.1743734927125919</v>
+        <v>1.174373492712592</v>
       </c>
       <c r="BB29" s="0">
         <v>0.74906367041198429</v>
@@ -10514,7 +10515,7 @@
         <v>0.67266894339232064</v>
       </c>
       <c r="BO29" s="0">
-        <v>1.1032308904649319</v>
+        <v>1.103230890464932</v>
       </c>
       <c r="BP29" s="0">
         <v>1.263962375073485</v>
@@ -10550,7 +10551,7 @@
         <v>0.56608741442864619</v>
       </c>
       <c r="CA29" s="0">
-        <v>0.25062656641603986</v>
+        <v>0.25062656641603987</v>
       </c>
       <c r="CB29" s="0">
         <v>0.78740157480314887</v>
@@ -10625,7 +10626,7 @@
         <v>3.7928519328956933</v>
       </c>
       <c r="CZ29" s="0">
-        <v>1.0331702011963015</v>
+        <v>1.0331702011963016</v>
       </c>
       <c r="DA29" s="0">
         <v>3.5302593659942332</v>
@@ -10741,13 +10742,13 @@
         <v>1.338538761851644</v>
       </c>
       <c r="V30" s="0">
-        <v>1.3020833333333321</v>
+        <v>1.3020833333333322</v>
       </c>
       <c r="W30" s="0">
         <v>1.3675213675213662</v>
       </c>
       <c r="X30" s="0">
-        <v>0.83380708736024189</v>
+        <v>0.8338070873602419</v>
       </c>
       <c r="Y30" s="0">
         <v>0.99580712788259873</v>
@@ -10831,7 +10832,7 @@
         <v>1.1054937647455332</v>
       </c>
       <c r="AZ30" s="0">
-        <v>1.0682969000864508</v>
+        <v>1.0682969000864509</v>
       </c>
       <c r="BA30" s="0">
         <v>1.2582573136206343</v>
@@ -10852,7 +10853,7 @@
         <v>0.66638900458142392</v>
       </c>
       <c r="BG30" s="0">
-        <v>0.48059149722735633</v>
+        <v>0.48059149722735634</v>
       </c>
       <c r="BH30" s="0">
         <v>1.3163766175814355</v>
@@ -10957,7 +10958,7 @@
         <v>1.357665520585382</v>
       </c>
       <c r="CP30" s="0">
-        <v>1.1472198904744761</v>
+        <v>1.1472198904744762</v>
       </c>
       <c r="CQ30" s="0">
         <v>1.5062852188990017</v>
@@ -10981,7 +10982,7 @@
         <v>1.6138818104598942</v>
       </c>
       <c r="CX30" s="0">
-        <v>2.8763183125599205</v>
+        <v>2.8763183125599206</v>
       </c>
       <c r="CY30" s="0">
         <v>3.4524677850717205</v>
@@ -11011,7 +11012,7 @@
         <v>1.3211382113821126</v>
       </c>
       <c r="DH30" s="0">
-        <v>2.7629233511586428</v>
+        <v>2.7629233511586429</v>
       </c>
       <c r="DI30" s="0">
         <v>1.2461059190031141</v>
@@ -11064,7 +11065,7 @@
         <v>0.32293874255727084</v>
       </c>
       <c r="I31" s="0">
-        <v>0.37098560354374271</v>
+        <v>0.37098560354374272</v>
       </c>
       <c r="J31" s="0">
         <v>0.37726197327194799</v>
@@ -11139,7 +11140,7 @@
         <v>1.1166440319903415</v>
       </c>
       <c r="AH31" s="0">
-        <v>0.5470980019029491</v>
+        <v>0.54709800190294911</v>
       </c>
       <c r="AI31" s="0">
         <v>1.1857707509881414</v>
@@ -11196,7 +11197,7 @@
         <v>1.1856243052982576</v>
       </c>
       <c r="BA31" s="0">
-        <v>1.1429170598720761</v>
+        <v>1.1429170598720762</v>
       </c>
       <c r="BB31" s="0">
         <v>0.95604178986792732</v>
@@ -11343,7 +11344,7 @@
         <v>2.2691420944060168</v>
       </c>
       <c r="CX31" s="0">
-        <v>4.1706615532118851</v>
+        <v>4.1706615532118852</v>
       </c>
       <c r="CY31" s="0">
         <v>2.96620471675176</v>
@@ -11432,7 +11433,7 @@
         <v>0.45399322207302384</v>
       </c>
       <c r="K32" s="0">
-        <v>0.43709616115545546</v>
+        <v>0.43709616115545547</v>
       </c>
       <c r="L32" s="0">
         <v>0.39069437044929967</v>
@@ -11456,7 +11457,7 @@
         <v>0.36730945821855016</v>
       </c>
       <c r="S32" s="0">
-        <v>0.74301105228940489</v>
+        <v>0.7430110522894049</v>
       </c>
       <c r="T32" s="0">
         <v>0.36194768831523699</v>
@@ -11615,7 +11616,7 @@
         <v>1.0783957348842874</v>
       </c>
       <c r="BT32" s="0">
-        <v>1.1447468837445975</v>
+        <v>1.1447468837445976</v>
       </c>
       <c r="BU32" s="0">
         <v>1.3470106724691779</v>
@@ -11696,7 +11697,7 @@
         <v>2.9235082098518306</v>
       </c>
       <c r="CU32" s="0">
-        <v>2.1956087824351362</v>
+        <v>2.1956087824351363</v>
       </c>
       <c r="CV32" s="0">
         <v>3.9800995024875734</v>
@@ -11711,7 +11712,7 @@
         <v>1.9207391198638517</v>
       </c>
       <c r="CZ32" s="0">
-        <v>3.3947020896450026</v>
+        <v>3.3947020896450027</v>
       </c>
       <c r="DA32" s="0">
         <v>3.4582132564841594</v>
@@ -11729,10 +11730,10 @@
         <v>1.5305300467214478</v>
       </c>
       <c r="DF32" s="0">
-        <v>2.0790729379686494</v>
+        <v>2.0790729379686495</v>
       </c>
       <c r="DG32" s="0">
-        <v>2.9471544715447235</v>
+        <v>2.9471544715447236</v>
       </c>
       <c r="DH32" s="0">
         <v>4.3672014260249679</v>
@@ -11800,7 +11801,7 @@
         <v>0.46172971053098877</v>
       </c>
       <c r="M33" s="0">
-        <v>0.65142065142065086</v>
+        <v>0.65142065142065087</v>
       </c>
       <c r="N33" s="0">
         <v>0.53997923156801619</v>
@@ -11818,7 +11819,7 @@
         <v>0.41322314049586739</v>
       </c>
       <c r="S33" s="0">
-        <v>0.70121668059812325</v>
+        <v>0.70121668059812326</v>
       </c>
       <c r="T33" s="0">
         <v>0.36194768831523566</v>
@@ -11914,7 +11915,7 @@
         <v>1.0432492656740597</v>
       </c>
       <c r="AY33" s="0">
-        <v>1.300977418267609</v>
+        <v>1.3009774182676091</v>
       </c>
       <c r="AZ33" s="0">
         <v>1.3091268371001594</v>
@@ -12028,7 +12029,7 @@
         <v>0.54817625975121187</v>
       </c>
       <c r="CK33" s="0">
-        <v>1.2374059883638417</v>
+        <v>1.2374059883638418</v>
       </c>
       <c r="CL33" s="0">
         <v>1.2220538082607038</v>
@@ -12049,7 +12050,7 @@
         <v>3.2184655396618957</v>
       </c>
       <c r="CR33" s="0">
-        <v>2.7378289123255541</v>
+        <v>2.7378289123255542</v>
       </c>
       <c r="CS33" s="0">
         <v>3.1623175586023855</v>
@@ -12189,7 +12190,7 @@
         <v>1.2084030488938453</v>
       </c>
       <c r="V34" s="0">
-        <v>1.4093137254901948</v>
+        <v>1.4093137254901949</v>
       </c>
       <c r="W34" s="0">
         <v>1.2136752136752125</v>
@@ -12255,7 +12256,7 @@
         <v>1.3447782546494982</v>
       </c>
       <c r="AR34" s="0">
-        <v>1.1713395638629271</v>
+        <v>1.1713395638629272</v>
       </c>
       <c r="AS34" s="0">
         <v>1.3888888888888875</v>
@@ -12297,7 +12298,7 @@
         <v>1.1408032505078909</v>
       </c>
       <c r="BF34" s="0">
-        <v>1.0134666111342487</v>
+        <v>1.0134666111342488</v>
       </c>
       <c r="BG34" s="0">
         <v>0.77634011090572941</v>
@@ -12324,7 +12325,7 @@
         <v>1.0452240505019137</v>
       </c>
       <c r="BO34" s="0">
-        <v>1.3846673421141495</v>
+        <v>1.3846673421141496</v>
       </c>
       <c r="BP34" s="0">
         <v>1.3521457965902397</v>
@@ -12345,7 +12346,7 @@
         <v>1.4299036369288145</v>
       </c>
       <c r="BV34" s="0">
-        <v>1.0483210483210474</v>
+        <v>1.0483210483210475</v>
       </c>
       <c r="BW34" s="0">
         <v>0.95029239766081786</v>
@@ -12390,7 +12391,7 @@
         <v>0.6325110689437059</v>
       </c>
       <c r="CK34" s="0">
-        <v>1.2374059883638417</v>
+        <v>1.2374059883638418</v>
       </c>
       <c r="CL34" s="0">
         <v>1.3073133762788922</v>
@@ -12453,7 +12454,7 @@
         <v>3.1255034638311558</v>
       </c>
       <c r="DF34" s="0">
-        <v>3.4935241990456682</v>
+        <v>3.4935241990456683</v>
       </c>
       <c r="DG34" s="0">
         <v>3.4552845528455252</v>
@@ -12521,7 +12522,7 @@
         <v>0.8741923223109076</v>
       </c>
       <c r="L35" s="0">
-        <v>0.58604155567394733</v>
+        <v>0.58604155567394734</v>
       </c>
       <c r="M35" s="0">
         <v>0.67914067914067855</v>
@@ -12569,13 +12570,13 @@
         <v>1.3192612137203155</v>
       </c>
       <c r="AB35" s="0">
-        <v>1.410177805027589</v>
+        <v>1.4101778050275891</v>
       </c>
       <c r="AC35" s="0">
         <v>1.27659574468085</v>
       </c>
       <c r="AD35" s="0">
-        <v>1.0706638115631681</v>
+        <v>1.0706638115631682</v>
       </c>
       <c r="AE35" s="0">
         <v>1.1612021857923487</v>
@@ -12647,7 +12648,7 @@
         <v>0.954178462828981</v>
       </c>
       <c r="BB35" s="0">
-        <v>1.0250344963532418</v>
+        <v>1.0250344963532419</v>
       </c>
       <c r="BC35" s="0">
         <v>1.1469443033688833</v>
@@ -12686,7 +12687,7 @@
         <v>1.2108040981061772</v>
       </c>
       <c r="BO35" s="0">
-        <v>1.3846673421141495</v>
+        <v>1.3846673421141496</v>
       </c>
       <c r="BP35" s="0">
         <v>1.3594944150499693</v>
@@ -12698,7 +12699,7 @@
         <v>1.4208444336804702</v>
       </c>
       <c r="BS35" s="0">
-        <v>0.94511086877499006</v>
+        <v>0.94511086877499007</v>
       </c>
       <c r="BT35" s="0">
         <v>0.85644026117188088</v>
@@ -12785,10 +12786,10 @@
         <v>3.5928143712574818</v>
       </c>
       <c r="CV35" s="0">
-        <v>2.1144278606965154</v>
+        <v>2.1144278606965155</v>
       </c>
       <c r="CW35" s="0">
-        <v>3.506855964082026</v>
+        <v>3.5068559640820261</v>
       </c>
       <c r="CX35" s="0">
         <v>3.179929689996801</v>
@@ -12800,7 +12801,7 @@
         <v>3.6510525906936966</v>
       </c>
       <c r="DA35" s="0">
-        <v>1.4649375600384233</v>
+        <v>1.4649375600384234</v>
       </c>
       <c r="DB35" s="0">
         <v>3.3176593521421078</v>
@@ -12812,10 +12813,10 @@
         <v>3.4001214329083154</v>
       </c>
       <c r="DE35" s="0">
-        <v>3.8827130658933426</v>
+        <v>3.8827130658933427</v>
       </c>
       <c r="DF35" s="0">
-        <v>3.9706884798909305</v>
+        <v>3.9706884798909306</v>
       </c>
       <c r="DG35" s="0">
         <v>3.3536585365853631</v>
@@ -12883,7 +12884,7 @@
         <v>0.81717977955150056</v>
       </c>
       <c r="L36" s="0">
-        <v>0.58604155567394733</v>
+        <v>0.58604155567394734</v>
       </c>
       <c r="M36" s="0">
         <v>0.92862092862092782</v>
@@ -13000,7 +13001,7 @@
         <v>1.0229919983794178</v>
       </c>
       <c r="AY36" s="0">
-        <v>1.4492753623188392</v>
+        <v>1.4492753623188393</v>
       </c>
       <c r="AZ36" s="0">
         <v>1.2906014573298743</v>
@@ -13114,7 +13115,7 @@
         <v>0.78009698503057068</v>
       </c>
       <c r="CK36" s="0">
-        <v>1.4360720874130823</v>
+        <v>1.4360720874130824</v>
       </c>
       <c r="CL36" s="0">
         <v>1.1873184286977381</v>
@@ -13126,7 +13127,7 @@
         <v>1.3998564249820518</v>
       </c>
       <c r="CO36" s="0">
-        <v>1.2254253724764161</v>
+        <v>1.2254253724764162</v>
       </c>
       <c r="CP36" s="0">
         <v>0.73150257824679155</v>
@@ -13254,7 +13255,7 @@
         <v>0.89304257528556519</v>
       </c>
       <c r="O37" s="0">
-        <v>1.0150945883593689</v>
+        <v>1.015094588359369</v>
       </c>
       <c r="P37" s="0">
         <v>0.99527953136552261</v>
@@ -13293,7 +13294,7 @@
         <v>1.1726766344180584</v>
       </c>
       <c r="AB37" s="0">
-        <v>1.410177805027589</v>
+        <v>1.4101778050275891</v>
       </c>
       <c r="AC37" s="0">
         <v>1.1347517730496444</v>
@@ -13413,7 +13414,7 @@
         <v>1.1144883485309007</v>
       </c>
       <c r="BP37" s="0">
-        <v>1.2492651381540258</v>
+        <v>1.2492651381540259</v>
       </c>
       <c r="BQ37" s="0">
         <v>1.5673606125867419</v>
@@ -13428,7 +13429,7 @@
         <v>0.73348596625116524</v>
       </c>
       <c r="BU37" s="0">
-        <v>1.1397782613200695</v>
+        <v>1.1397782613200696</v>
       </c>
       <c r="BV37" s="0">
         <v>1.2776412776412767</v>
@@ -13533,7 +13534,7 @@
         <v>2.5445292620865119</v>
       </c>
       <c r="DD37" s="0">
-        <v>2.1857923497267739</v>
+        <v>2.185792349726774</v>
       </c>
       <c r="DE37" s="0">
         <v>3.963267278878682</v>
@@ -13580,7 +13581,7 @@
         <v>0.99514969058371616</v>
       </c>
       <c r="C38" s="0">
-        <v>1.0369715716600449</v>
+        <v>1.036971571660045</v>
       </c>
       <c r="D38" s="0">
         <v>0.94254569297599167</v>
@@ -13652,7 +13653,7 @@
         <v>1.0295126973232738</v>
       </c>
       <c r="AA38" s="0">
-        <v>0.87950747581355015</v>
+        <v>0.87950747581355016</v>
       </c>
       <c r="AB38" s="0">
         <v>1.3693030860412925</v>
@@ -13892,7 +13893,7 @@
         <v>3.8662486938349256</v>
       </c>
       <c r="DC38" s="0">
-        <v>1.6389762011675006</v>
+        <v>1.6389762011675007</v>
       </c>
       <c r="DD38" s="0">
         <v>1.5543412264723842</v>
@@ -13910,7 +13911,7 @@
         <v>0.44563279857397792</v>
       </c>
       <c r="DI38" s="0">
-        <v>1.5576323987539042</v>
+        <v>1.5576323987539043</v>
       </c>
       <c r="DJ38" s="0">
         <v>0.81300813008130612</v>
@@ -13928,7 +13929,7 @@
         <v>0.5208333333333367</v>
       </c>
       <c r="DO38" s="0">
-        <v>1.6181229773462888</v>
+        <v>1.6181229773462889</v>
       </c>
       <c r="DP38" s="0">
         <v>1.8779342723004817</v>
@@ -13942,7 +13943,7 @@
         <v>1.1707643418631868</v>
       </c>
       <c r="C39" s="0">
-        <v>1.1371335984681092</v>
+        <v>1.1371335984681093</v>
       </c>
       <c r="D39" s="0">
         <v>1.06275441903669</v>
@@ -14029,7 +14030,7 @@
         <v>0.81967213114754023</v>
       </c>
       <c r="AF39" s="0">
-        <v>1.3333333333333321</v>
+        <v>1.3333333333333322</v>
       </c>
       <c r="AG39" s="0">
         <v>1.2826316583672841</v>
@@ -14098,7 +14099,7 @@
         <v>1.2714370195150788</v>
       </c>
       <c r="BC39" s="0">
-        <v>0.87184696123243532</v>
+        <v>0.87184696123243533</v>
       </c>
       <c r="BD39" s="0">
         <v>1.0620075368276798</v>
@@ -14155,7 +14156,7 @@
         <v>1.1915863641073454</v>
       </c>
       <c r="BV39" s="0">
-        <v>1.3759213759213746</v>
+        <v>1.3759213759213747</v>
       </c>
       <c r="BW39" s="0">
         <v>0.6140350877192976</v>
@@ -14206,7 +14207,7 @@
         <v>1.0578501957812294</v>
       </c>
       <c r="CM39" s="0">
-        <v>0.96888392025339964</v>
+        <v>0.96888392025339965</v>
       </c>
       <c r="CN39" s="0">
         <v>1.1605647284039236</v>
@@ -14284,10 +14285,10 @@
         <v>0.13054830287206254</v>
       </c>
       <c r="DM39" s="0">
-        <v>1.282051282051281</v>
+        <v>1.2820512820512811</v>
       </c>
       <c r="DN39" s="0">
-        <v>0.58593749999999944</v>
+        <v>0.58593749999999945</v>
       </c>
       <c r="DO39" s="0">
         <v>0.88996763754045227</v>
@@ -14391,7 +14392,7 @@
         <v>1.2295081967213104</v>
       </c>
       <c r="AF40" s="0">
-        <v>1.3333333333333321</v>
+        <v>1.3333333333333322</v>
       </c>
       <c r="AG40" s="0">
         <v>1.2977214425833701</v>
@@ -14496,7 +14497,7 @@
         <v>1.3246403808341083</v>
       </c>
       <c r="BO40" s="0">
-        <v>1.1032308904649319</v>
+        <v>1.103230890464932</v>
       </c>
       <c r="BP40" s="0">
         <v>1.1684303350970007</v>
@@ -14541,7 +14542,7 @@
         <v>0.72490938632670854</v>
       </c>
       <c r="CD40" s="0">
-        <v>0.8846153846153838</v>
+        <v>0.88461538461538381</v>
       </c>
       <c r="CE40" s="0">
         <v>0.88888888888888817</v>
@@ -14556,7 +14557,7 @@
         <v>1.2322777262488396</v>
       </c>
       <c r="CI40" s="0">
-        <v>1.3422074320576804</v>
+        <v>1.3422074320576805</v>
       </c>
       <c r="CJ40" s="0">
         <v>1.2861058401855354</v>
@@ -14568,7 +14569,7 @@
         <v>0.86838448907414345</v>
       </c>
       <c r="CM40" s="0">
-        <v>1.3787963480529148</v>
+        <v>1.3787963480529149</v>
       </c>
       <c r="CN40" s="0">
         <v>1.0887772194304848</v>
@@ -14583,7 +14584,7 @@
         <v>1.3058084091894224</v>
       </c>
       <c r="CR40" s="0">
-        <v>1.7577500798977292</v>
+        <v>1.7577500798977293</v>
       </c>
       <c r="CS40" s="0">
         <v>1.4005602240896347</v>
@@ -14762,7 +14763,7 @@
         <v>1.2844909609895325</v>
       </c>
       <c r="AI41" s="0">
-        <v>1.3175230566534903</v>
+        <v>1.3175230566534904</v>
       </c>
       <c r="AJ41" s="0">
         <v>0.80495356037151633</v>
@@ -14897,7 +14898,7 @@
         <v>1.5037593984962392</v>
       </c>
       <c r="CB41" s="0">
-        <v>1.5223097112860879</v>
+        <v>1.522309711286088</v>
       </c>
       <c r="CC41" s="0">
         <v>0.77490313710786085</v>
@@ -14909,7 +14910,7 @@
         <v>0.7619047619047612</v>
       </c>
       <c r="CF41" s="0">
-        <v>1.4968336211859516</v>
+        <v>1.4968336211859517</v>
       </c>
       <c r="CG41" s="0">
         <v>1.2290964958931621</v>
@@ -14927,7 +14928,7 @@
         <v>1.2459202497516664</v>
       </c>
       <c r="CL41" s="0">
-        <v>0.81154477706201777</v>
+        <v>0.81154477706201778</v>
       </c>
       <c r="CM41" s="0">
         <v>1.173840134153157</v>
@@ -14981,7 +14982,7 @@
         <v>0.34425984134111631</v>
       </c>
       <c r="DD41" s="0">
-        <v>0.21857923497267739</v>
+        <v>0.2185792349726774</v>
       </c>
       <c r="DE41" s="0">
         <v>1.6916384726921203</v>
@@ -15008,7 +15009,7 @@
         <v>0.087032201914708368</v>
       </c>
       <c r="DM41" s="0">
-        <v>0.49857549857549815</v>
+        <v>0.49857549857549816</v>
       </c>
       <c r="DN41" s="0">
         <v>0.19531249999999983</v>
@@ -15046,7 +15047,7 @@
         <v>1.1000100918357039</v>
       </c>
       <c r="I42" s="0">
-        <v>1.1184939091915826</v>
+        <v>1.1184939091915827</v>
       </c>
       <c r="J42" s="0">
         <v>1.2980369588848382</v>
@@ -15073,7 +15074,7 @@
         <v>0.87448559670781811</v>
       </c>
       <c r="R42" s="0">
-        <v>1.7906336088154255</v>
+        <v>1.7906336088154256</v>
       </c>
       <c r="S42" s="0">
         <v>1.2538311507383662</v>
@@ -15085,7 +15086,7 @@
         <v>1.0782673359360466</v>
       </c>
       <c r="V42" s="0">
-        <v>0.61274509803921517</v>
+        <v>0.61274509803921518</v>
       </c>
       <c r="W42" s="0">
         <v>0.58119658119658069</v>
@@ -15109,7 +15110,7 @@
         <v>0.73286052009456204</v>
       </c>
       <c r="AD42" s="0">
-        <v>0.54722817035450821</v>
+        <v>0.54722817035450822</v>
       </c>
       <c r="AE42" s="0">
         <v>1.0245901639344253</v>
@@ -15118,7 +15119,7 @@
         <v>1.1228070175438587</v>
       </c>
       <c r="AG42" s="0">
-        <v>1.1468236004225127</v>
+        <v>1.1468236004225128</v>
       </c>
       <c r="AH42" s="0">
         <v>1.4827148747224852</v>
@@ -15136,7 +15137,7 @@
         <v>1.2703940156058542</v>
       </c>
       <c r="AM42" s="0">
-        <v>0.77232004942848242</v>
+        <v>0.77232004942848243</v>
       </c>
       <c r="AN42" s="0">
         <v>0.6953498478922201</v>
@@ -15304,7 +15305,7 @@
         <v>0.21985050165887177</v>
       </c>
       <c r="CQ42" s="0">
-        <v>0.34677069787602915</v>
+        <v>0.34677069787602916</v>
       </c>
       <c r="CR42" s="0">
         <v>0.74571215510812761</v>
@@ -15507,7 +15508,7 @@
         <v>0.62921348314606684</v>
       </c>
       <c r="AP43" s="0">
-        <v>0.85356880058866746</v>
+        <v>0.85356880058866747</v>
       </c>
       <c r="AQ43" s="0">
         <v>0.71530758226037128</v>
@@ -15525,7 +15526,7 @@
         <v>1.1931256181998011</v>
       </c>
       <c r="AV43" s="0">
-        <v>0.96132349653476334</v>
+        <v>0.96132349653476335</v>
       </c>
       <c r="AW43" s="0">
         <v>0.91496232508073116</v>
@@ -15558,7 +15559,7 @@
         <v>1.2772455921143957</v>
       </c>
       <c r="BG43" s="0">
-        <v>1.2076401725200236</v>
+        <v>1.2076401725200237</v>
       </c>
       <c r="BH43" s="0">
         <v>0.66376617581436803</v>
@@ -15594,13 +15595,13 @@
         <v>1.1705820618390237</v>
       </c>
       <c r="BS43" s="0">
-        <v>0.27868653822852268</v>
+        <v>0.27868653822852269</v>
       </c>
       <c r="BT43" s="0">
         <v>0.3137454422114811</v>
       </c>
       <c r="BU43" s="0">
-        <v>0.80820640348150385</v>
+        <v>0.80820640348150386</v>
       </c>
       <c r="BV43" s="0">
         <v>1.523341523341522</v>
@@ -15693,7 +15694,7 @@
         <v>0</v>
       </c>
       <c r="CZ43" s="0">
-        <v>0.155363940029519</v>
+        <v>0.15536394002951901</v>
       </c>
       <c r="DA43" s="0">
         <v>0.024015369836695461</v>
@@ -15782,7 +15783,7 @@
         <v>1.2786361214704305</v>
       </c>
       <c r="M44" s="0">
-        <v>1.455301455301454</v>
+        <v>1.4553014553014541</v>
       </c>
       <c r="N44" s="0">
         <v>1.4018691588785033</v>
@@ -15803,7 +15804,7 @@
         <v>1.2259682362775135</v>
       </c>
       <c r="T44" s="0">
-        <v>1.2497439049375116</v>
+        <v>1.2497439049375117</v>
       </c>
       <c r="U44" s="0">
         <v>0.59490611637850854</v>
@@ -15818,7 +15819,7 @@
         <v>1.1180595035057788</v>
       </c>
       <c r="Y44" s="0">
-        <v>0.68134171907756746</v>
+        <v>0.68134171907756747</v>
       </c>
       <c r="Z44" s="0">
         <v>1.4184397163120555</v>
@@ -15974,7 +15975,7 @@
         <v>1.0938157341186361</v>
       </c>
       <c r="BY44" s="0">
-        <v>1.184503901895205</v>
+        <v>1.1845039018952051</v>
       </c>
       <c r="BZ44" s="0">
         <v>1.2769878883622949</v>
@@ -15995,10 +15996,10 @@
         <v>1.0158730158730149</v>
       </c>
       <c r="CF44" s="0">
-        <v>1.4968336211859516</v>
+        <v>1.4968336211859517</v>
       </c>
       <c r="CG44" s="0">
-        <v>1.0518229628316484</v>
+        <v>1.0518229628316485</v>
       </c>
       <c r="CH44" s="0">
         <v>1.0997747449317601</v>
@@ -16007,7 +16008,7 @@
         <v>1.2978369384359389</v>
       </c>
       <c r="CJ44" s="0">
-        <v>1.5496521189120795</v>
+        <v>1.5496521189120796</v>
       </c>
       <c r="CK44" s="0">
         <v>1.1068539804171977</v>
@@ -16022,7 +16023,7 @@
         <v>0.90930844699688851</v>
       </c>
       <c r="CO44" s="0">
-        <v>0.46724852331834565</v>
+        <v>0.46724852331834566</v>
       </c>
       <c r="CP44" s="0">
         <v>0.14789942838869555</v>
@@ -16120,7 +16121,7 @@
         <v>1.4206485807174263</v>
       </c>
       <c r="E45" s="0">
-        <v>1.2615643397813276</v>
+        <v>1.2615643397813277</v>
       </c>
       <c r="F45" s="0">
         <v>1.3772918998020132</v>
@@ -16135,7 +16136,7 @@
         <v>1.4728682170542622</v>
       </c>
       <c r="J45" s="0">
-        <v>1.3875567491527578</v>
+        <v>1.3875567491527579</v>
       </c>
       <c r="K45" s="0">
         <v>1.2162675788673498</v>
@@ -16150,10 +16151,10 @@
         <v>1.1838006230529585</v>
       </c>
       <c r="O45" s="0">
-        <v>1.2392063805945543</v>
+        <v>1.2392063805945544</v>
       </c>
       <c r="P45" s="0">
-        <v>1.2398339305010508</v>
+        <v>1.2398339305010509</v>
       </c>
       <c r="Q45" s="0">
         <v>1.1831275720164598</v>
@@ -16180,7 +16181,7 @@
         <v>1.1749099867348862</v>
       </c>
       <c r="Y45" s="0">
-        <v>0.44549266247379415</v>
+        <v>0.44549266247379416</v>
       </c>
       <c r="Z45" s="0">
         <v>1.3726835964310213</v>
@@ -16237,7 +16238,7 @@
         <v>0.72961373390557871</v>
       </c>
       <c r="AR45" s="0">
-        <v>1.0965732087227404</v>
+        <v>1.0965732087227405</v>
       </c>
       <c r="AS45" s="0">
         <v>0.79365079365079294</v>
@@ -16264,7 +16265,7 @@
         <v>0.87069284920340784</v>
       </c>
       <c r="BA45" s="0">
-        <v>0.220195029883611</v>
+        <v>0.22019502988361101</v>
       </c>
       <c r="BB45" s="0">
         <v>1.094027202838556</v>
@@ -16309,7 +16310,7 @@
         <v>0.63041765169424691</v>
       </c>
       <c r="BP45" s="0">
-        <v>0.63932980599647204</v>
+        <v>0.63932980599647205</v>
       </c>
       <c r="BQ45" s="0">
         <v>0.87341469251016912</v>
@@ -16357,16 +16358,16 @@
         <v>1.1428571428571419</v>
       </c>
       <c r="CF45" s="0">
-        <v>1.4968336211859516</v>
+        <v>1.4968336211859517</v>
       </c>
       <c r="CG45" s="0">
-        <v>1.1109141405188196</v>
+        <v>1.1109141405188197</v>
       </c>
       <c r="CH45" s="0">
         <v>1.1306921072390785</v>
       </c>
       <c r="CI45" s="0">
-        <v>1.3422074320576804</v>
+        <v>1.3422074320576805</v>
       </c>
       <c r="CJ45" s="0">
         <v>1.3704406493780297</v>
@@ -16515,7 +16516,7 @@
         <v>1.1996572407883541</v>
       </c>
       <c r="P46" s="0">
-        <v>1.3251436046181055</v>
+        <v>1.3251436046181056</v>
       </c>
       <c r="Q46" s="0">
         <v>1.5946502057613272</v>
@@ -16542,10 +16543,10 @@
         <v>0.92855789274209444</v>
       </c>
       <c r="Y46" s="0">
-        <v>0.44549266247379748</v>
+        <v>0.44549266247379749</v>
       </c>
       <c r="Z46" s="0">
-        <v>1.3955616563715489</v>
+        <v>1.395561656371549</v>
       </c>
       <c r="AA46" s="0">
         <v>0.49838756962767838</v>
@@ -16560,13 +16561,13 @@
         <v>0.26171782060433191</v>
       </c>
       <c r="AE46" s="0">
-        <v>0.81967213114754633</v>
+        <v>0.81967213114754634</v>
       </c>
       <c r="AF46" s="0">
         <v>0.42105263157895012</v>
       </c>
       <c r="AG46" s="0">
-        <v>0.82239323977667655</v>
+        <v>0.82239323977667656</v>
       </c>
       <c r="AH46" s="0">
         <v>1.3637805264827239</v>
@@ -16650,7 +16651,7 @@
         <v>0.36256135653726251</v>
       </c>
       <c r="BI46" s="0">
-        <v>0.77461000537924118</v>
+        <v>0.77461000537924119</v>
       </c>
       <c r="BJ46" s="0">
         <v>0.54542104293348426</v>
@@ -16689,7 +16690,7 @@
         <v>0.58025075121749414</v>
       </c>
       <c r="BV46" s="0">
-        <v>1.2285012285012364</v>
+        <v>1.2285012285012365</v>
       </c>
       <c r="BW46" s="0">
         <v>0.27777777777777957</v>
@@ -16713,13 +16714,13 @@
         <v>0.44994375703037415</v>
       </c>
       <c r="CD46" s="0">
-        <v>0.38461538461538713</v>
+        <v>0.38461538461538714</v>
       </c>
       <c r="CE46" s="0">
-        <v>1.5873015873015976</v>
+        <v>1.5873015873015977</v>
       </c>
       <c r="CF46" s="0">
-        <v>1.7271157167530335</v>
+        <v>1.7271157167530336</v>
       </c>
       <c r="CG46" s="0">
         <v>1.3236423801926458</v>
@@ -16934,7 +16935,7 @@
         <v>1.1417697431018068</v>
       </c>
       <c r="AI47" s="0">
-        <v>0.83105300496604761</v>
+        <v>0.83105300496604762</v>
       </c>
       <c r="AJ47" s="0">
         <v>0.42311661506707909</v>
@@ -17003,7 +17004,7 @@
         <v>0.21878418502891056</v>
       </c>
       <c r="BF47" s="0">
-        <v>1.0134666111342487</v>
+        <v>1.0134666111342488</v>
       </c>
       <c r="BG47" s="0">
         <v>1.2322858903265548</v>
@@ -17024,7 +17025,7 @@
         <v>1.337409247229651</v>
       </c>
       <c r="BM47" s="0">
-        <v>0.15644011819920028</v>
+        <v>0.15644011819920029</v>
       </c>
       <c r="BN47" s="0">
         <v>1.2211528510814438</v>
@@ -17057,7 +17058,7 @@
         <v>0.20467836257309924</v>
       </c>
       <c r="BX47" s="0">
-        <v>0.77128032534006385</v>
+        <v>0.77128032534006386</v>
       </c>
       <c r="BY47" s="0">
         <v>1.0451505016722398</v>
@@ -17227,10 +17228,10 @@
         <v>1.2732801216267569</v>
       </c>
       <c r="L48" s="0">
-        <v>1.5982951518380379</v>
+        <v>1.598295151838038</v>
       </c>
       <c r="M48" s="0">
-        <v>1.2889812889812879</v>
+        <v>1.288981288981288</v>
       </c>
       <c r="N48" s="0">
         <v>1.194184839044651</v>
@@ -17401,7 +17402,7 @@
         <v>0.47858339315625703</v>
       </c>
       <c r="BR48" s="0">
-        <v>0.80729797368208533</v>
+        <v>0.80729797368208534</v>
       </c>
       <c r="BS48" s="0">
         <v>0.09693444807948616</v>
@@ -17601,7 +17602,7 @@
         <v>1.1864741941862753</v>
       </c>
       <c r="P49" s="0">
-        <v>1.2398339305010508</v>
+        <v>1.2398339305010509</v>
       </c>
       <c r="Q49" s="0">
         <v>1.1831275720164598</v>
@@ -17655,10 +17656,10 @@
         <v>0.68658518183189921</v>
       </c>
       <c r="AH49" s="0">
-        <v>1.2369172216936239</v>
+        <v>1.236917221693624</v>
       </c>
       <c r="AI49" s="0">
-        <v>0.90199655417046642</v>
+        <v>0.90199655417046643</v>
       </c>
       <c r="AJ49" s="0">
         <v>0.22703818369453024</v>
@@ -17670,7 +17671,7 @@
         <v>0.8641258786354542</v>
       </c>
       <c r="AM49" s="0">
-        <v>0.52517763361136804</v>
+        <v>0.52517763361136805</v>
       </c>
       <c r="AN49" s="0">
         <v>0.30421555845284631</v>
@@ -17730,10 +17731,10 @@
         <v>0.79133694294044077</v>
       </c>
       <c r="BG49" s="0">
-        <v>1.2014787430683906</v>
+        <v>1.2014787430683907</v>
       </c>
       <c r="BH49" s="0">
-        <v>0.27331548415885742</v>
+        <v>0.27331548415885743</v>
       </c>
       <c r="BI49" s="0">
         <v>0.47337278106508829</v>
@@ -17802,10 +17803,10 @@
         <v>0.269230769230769</v>
       </c>
       <c r="CE49" s="0">
-        <v>1.3333333333333321</v>
+        <v>1.3333333333333322</v>
       </c>
       <c r="CF49" s="0">
-        <v>0.80598733448474313</v>
+        <v>0.80598733448474314</v>
       </c>
       <c r="CG49" s="0">
         <v>0.97500443183832575</v>
@@ -17814,7 +17815,7 @@
         <v>0.75085022746345054</v>
       </c>
       <c r="CI49" s="0">
-        <v>1.2090959511924559</v>
+        <v>1.209095951192456</v>
       </c>
       <c r="CJ49" s="0">
         <v>1.2650221378874118</v>
@@ -17924,7 +17925,7 @@
         <v>1.233483860177286</v>
       </c>
       <c r="C50" s="0">
-        <v>1.1371335984681092</v>
+        <v>1.1371335984681093</v>
       </c>
       <c r="D50" s="0">
         <v>1.1720350790918768</v>
@@ -18056,7 +18057,7 @@
         <v>0.16694490818030036</v>
       </c>
       <c r="AU50" s="0">
-        <v>0.6985657764589509</v>
+        <v>0.69856577645895091</v>
       </c>
       <c r="AV50" s="0">
         <v>0.40241448692152881</v>
@@ -18134,7 +18135,7 @@
         <v>0.089035868735690582</v>
       </c>
       <c r="BU50" s="0">
-        <v>0.34193347839602078</v>
+        <v>0.34193347839602079</v>
       </c>
       <c r="BV50" s="0">
         <v>0.96642096642096553</v>
@@ -18176,7 +18177,7 @@
         <v>0.66693167262930031</v>
       </c>
       <c r="CI50" s="0">
-        <v>0.97615085967831305</v>
+        <v>0.97615085967831306</v>
       </c>
       <c r="CJ50" s="0">
         <v>1.1806873286949178</v>
@@ -18292,7 +18293,7 @@
         <v>1.1774991120946359</v>
       </c>
       <c r="E51" s="0">
-        <v>1.1992648662118794</v>
+        <v>1.1992648662118795</v>
       </c>
       <c r="F51" s="0">
         <v>1.0071447017302222</v>
@@ -18325,7 +18326,7 @@
         <v>0.96236240195109002</v>
       </c>
       <c r="P51" s="0">
-        <v>1.1886481260308241</v>
+        <v>1.1886481260308242</v>
       </c>
       <c r="Q51" s="0">
         <v>1.028806584362139</v>
@@ -18684,7 +18685,7 @@
         <v>1.0072689511941839</v>
       </c>
       <c r="O52" s="0">
-        <v>0.9096302155428112</v>
+        <v>0.90963021554281121</v>
       </c>
       <c r="P52" s="0">
         <v>1.1260876983449915</v>
@@ -18807,7 +18808,7 @@
         <v>0.13120027086507521</v>
       </c>
       <c r="BD52" s="0">
-        <v>0.13018156903048977</v>
+        <v>0.13018156903048978</v>
       </c>
       <c r="BE52" s="0">
         <v>0.078137208938896641</v>
@@ -18843,7 +18844,7 @@
         <v>0.36023865811099826</v>
       </c>
       <c r="BP52" s="0">
-        <v>0.27189888300999387</v>
+        <v>0.27189888300999388</v>
       </c>
       <c r="BQ52" s="0">
         <v>0.11964584828906426</v>
@@ -19181,7 +19182,7 @@
         <v>0.76401725200246384</v>
       </c>
       <c r="BH53" s="0">
-        <v>0.066934404283801804</v>
+        <v>0.066934404283801805</v>
       </c>
       <c r="BI53" s="0">
         <v>0.27613412228796819</v>
@@ -19253,7 +19254,7 @@
         <v>1.2063492063492052</v>
       </c>
       <c r="CF53" s="0">
-        <v>0.80598733448474313</v>
+        <v>0.80598733448474314</v>
       </c>
       <c r="CG53" s="0">
         <v>0.71500325001477216</v>
@@ -19369,7 +19370,7 @@
         <v>0.82115686511290831</v>
       </c>
       <c r="B54" s="0">
-        <v>0.94915537715336928</v>
+        <v>0.94915537715336929</v>
       </c>
       <c r="C54" s="0">
         <v>0.74532331713065192</v>
@@ -19588,7 +19589,7 @@
         <v>0.72072072072072013</v>
       </c>
       <c r="BW54" s="0">
-        <v>0.04385964912280698</v>
+        <v>0.043859649122806981</v>
       </c>
       <c r="BX54" s="0">
         <v>0.33655868742111872</v>
@@ -19612,7 +19613,7 @@
         <v>0.076923076923076858</v>
       </c>
       <c r="CE54" s="0">
-        <v>1.3333333333333321</v>
+        <v>1.3333333333333322</v>
       </c>
       <c r="CF54" s="0">
         <v>0.74841681059297582</v>
@@ -19758,7 +19759,7 @@
         <v>0.93995779781316557</v>
       </c>
       <c r="K55" s="0">
-        <v>0.74116305587229669</v>
+        <v>0.7411630558722967</v>
       </c>
       <c r="L55" s="0">
         <v>1.1188066062866349</v>
@@ -19881,7 +19882,7 @@
         <v>0.13481631277384651</v>
       </c>
       <c r="AZ55" s="0">
-        <v>0.27170556996418604</v>
+        <v>0.27170556996418605</v>
       </c>
       <c r="BA55" s="0">
         <v>0.031456432840516094</v>
@@ -19944,7 +19945,7 @@
         <v>0.021199016365640776</v>
       </c>
       <c r="BU55" s="0">
-        <v>0.082892964459642018</v>
+        <v>0.082892964459642019</v>
       </c>
       <c r="BV55" s="0">
         <v>0.67158067158067603</v>
@@ -19986,7 +19987,7 @@
         <v>0.27825626076586901</v>
       </c>
       <c r="CI55" s="0">
-        <v>0.4769828064337247</v>
+        <v>0.47698280643372471</v>
       </c>
       <c r="CJ55" s="0">
         <v>0.81172253847776199</v>
@@ -20004,7 +20005,7 @@
         <v>0.23929169657813029</v>
       </c>
       <c r="CO55" s="0">
-        <v>0.057304064180552255</v>
+        <v>0.057304064180552256</v>
       </c>
       <c r="CP55" s="0">
         <v>0.011991845545029458</v>
@@ -20135,7 +20136,7 @@
         <v>0.72506756311383491</v>
       </c>
       <c r="P56" s="0">
-        <v>0.79622362509241817</v>
+        <v>0.79622362509241818</v>
       </c>
       <c r="Q56" s="0">
         <v>0.72016460905349722</v>
@@ -20192,7 +20193,7 @@
         <v>0.70567713288931111</v>
       </c>
       <c r="AI56" s="0">
-        <v>0.25336981858720969</v>
+        <v>0.2533698185872097</v>
       </c>
       <c r="AJ56" s="0">
         <v>0.051599587203302329</v>
@@ -20267,7 +20268,7 @@
         <v>0.67159581022797221</v>
       </c>
       <c r="BH56" s="0">
-        <v>0.066934404283801804</v>
+        <v>0.066934404283801805</v>
       </c>
       <c r="BI56" s="0">
         <v>0.15420476958938484</v>
@@ -20297,13 +20298,13 @@
         <v>0.095716678631251412</v>
       </c>
       <c r="BR56" s="0">
-        <v>0.23411641236780475</v>
+        <v>0.23411641236780476</v>
       </c>
       <c r="BS56" s="0">
         <v>0.0080778706732905128</v>
       </c>
       <c r="BT56" s="0">
-        <v>0.0084796065462562457</v>
+        <v>0.0084796065462562458</v>
       </c>
       <c r="BU56" s="0">
         <v>0.093254585017096603</v>
@@ -20351,7 +20352,7 @@
         <v>0.46589018302828578</v>
       </c>
       <c r="CJ56" s="0">
-        <v>0.71684587813620015</v>
+        <v>0.71684587813620016</v>
       </c>
       <c r="CK56" s="0">
         <v>0.30083723570313581</v>
@@ -20452,10 +20453,10 @@
     </row>
     <row r="57">
       <c r="A57" s="0">
-        <v>0.70844906009741115</v>
+        <v>0.70844906009741116</v>
       </c>
       <c r="B57" s="0">
-        <v>0.62719518314099298</v>
+        <v>0.62719518314099299</v>
       </c>
       <c r="C57" s="0">
         <v>0.57445868316394111</v>
@@ -20467,7 +20468,7 @@
         <v>0.78185839329657592</v>
       </c>
       <c r="F57" s="0">
-        <v>0.62552007116008101</v>
+        <v>0.62552007116008102</v>
       </c>
       <c r="G57" s="0">
         <v>0.94818376068375987</v>
@@ -20581,7 +20582,7 @@
         <v>0.042918454935622283</v>
       </c>
       <c r="AR57" s="0">
-        <v>0.2367601246105917</v>
+        <v>0.23676012461059171</v>
       </c>
       <c r="AS57" s="0">
         <v>0.33068783068783036</v>
@@ -20632,7 +20633,7 @@
         <v>0.06135653726015166</v>
       </c>
       <c r="BI57" s="0">
-        <v>0.15779092702169611</v>
+        <v>0.15779092702169612</v>
       </c>
       <c r="BJ57" s="0">
         <v>0.051593882439653536</v>
@@ -20659,7 +20660,7 @@
         <v>0.095716678631251412</v>
       </c>
       <c r="BR57" s="0">
-        <v>0.28255429078872984</v>
+        <v>0.28255429078872985</v>
       </c>
       <c r="BS57" s="0">
         <v>0.020194676683226286</v>
@@ -20719,7 +20720,7 @@
         <v>0.17312331488576685</v>
       </c>
       <c r="CL57" s="0">
-        <v>0.047366426676771461</v>
+        <v>0.047366426676771462</v>
       </c>
       <c r="CM57" s="0">
         <v>0.27948574622694217</v>
@@ -20823,7 +20824,7 @@
         <v>0.5008101340403589</v>
       </c>
       <c r="D58" s="0">
-        <v>0.66388000983525874</v>
+        <v>0.66388000983525875</v>
       </c>
       <c r="E58" s="0">
         <v>0.7912033143319932</v>
@@ -20943,7 +20944,7 @@
         <v>0.071530758226037133</v>
       </c>
       <c r="AR58" s="0">
-        <v>0.2367601246105917</v>
+        <v>0.23676012461059171</v>
       </c>
       <c r="AS58" s="0">
         <v>0.19841269841269824</v>
@@ -20985,7 +20986,7 @@
         <v>0</v>
       </c>
       <c r="BF58" s="0">
-        <v>0.29154518950437291</v>
+        <v>0.29154518950437292</v>
       </c>
       <c r="BG58" s="0">
         <v>0.48675292667898912</v>
@@ -21027,7 +21028,7 @@
         <v>0.0080778706732905128</v>
       </c>
       <c r="BT58" s="0">
-        <v>0.016959213092512491</v>
+        <v>0.016959213092512492</v>
       </c>
       <c r="BU58" s="0">
         <v>0.041446482229820704</v>
@@ -21054,7 +21055,7 @@
         <v>0.26246719160104964</v>
       </c>
       <c r="CC58" s="0">
-        <v>0.024996875390576156</v>
+        <v>0.024996875390576157</v>
       </c>
       <c r="CD58" s="0">
         <v>0.01282051282051281</v>
@@ -21215,7 +21216,7 @@
         <v>0.42966042966042928</v>
       </c>
       <c r="N59" s="0">
-        <v>0.61266874350986444</v>
+        <v>0.61266874350986445</v>
       </c>
       <c r="O59" s="0">
         <v>0.47458967767451016</v>
@@ -21296,7 +21297,7 @@
         <v>0</v>
       </c>
       <c r="AO59" s="0">
-        <v>0.089887640449438116</v>
+        <v>0.089887640449438117</v>
       </c>
       <c r="AP59" s="0">
         <v>0.029433406916850598</v>
@@ -21341,13 +21342,13 @@
         <v>0.012696800406297603</v>
       </c>
       <c r="BD59" s="0">
-        <v>0.020554984583761544</v>
+        <v>0.020554984583761545</v>
       </c>
       <c r="BE59" s="0">
         <v>0.015627441787779327</v>
       </c>
       <c r="BF59" s="0">
-        <v>0.2637789809801469</v>
+        <v>0.26377898098014691</v>
       </c>
       <c r="BG59" s="0">
         <v>0.45594577942082526</v>
@@ -21398,7 +21399,7 @@
         <v>0.26208026208026186</v>
       </c>
       <c r="BW59" s="0">
-        <v>0.04385964912280698</v>
+        <v>0.043859649122806981</v>
       </c>
       <c r="BX59" s="0">
         <v>0.098162950497826307</v>
@@ -21604,7 +21605,7 @@
         <v>0</v>
       </c>
       <c r="W60" s="0">
-        <v>0.085470085470085388</v>
+        <v>0.085470085470085389</v>
       </c>
       <c r="X60" s="0">
         <v>0.28425241614553698</v>
@@ -21727,7 +21728,7 @@
         <v>0</v>
       </c>
       <c r="BL60" s="0">
-        <v>0.48401477518787372</v>
+        <v>0.48401477518787373</v>
       </c>
       <c r="BM60" s="0">
         <v>0.011588156903644465</v>
@@ -21915,7 +21916,7 @@
         <v>0.52331557798336559</v>
       </c>
       <c r="F61" s="0">
-        <v>0.37588591432096607</v>
+        <v>0.37588591432096608</v>
       </c>
       <c r="G61" s="0">
         <v>0.6143162393162388</v>
@@ -22137,10 +22138,10 @@
         <v>0.30075187969924788</v>
       </c>
       <c r="CB61" s="0">
-        <v>0.052493438320209924</v>
+        <v>0.052493438320209925</v>
       </c>
       <c r="CC61" s="0">
-        <v>0.024996875390576156</v>
+        <v>0.024996875390576157</v>
       </c>
       <c r="CD61" s="0">
         <v>0.038461538461538429</v>
@@ -22499,7 +22500,7 @@
         <v>0.15037593984962394</v>
       </c>
       <c r="CB62" s="0">
-        <v>0.052493438320209924</v>
+        <v>0.052493438320209925</v>
       </c>
       <c r="CC62" s="0">
         <v>0.037495313085864235</v>
@@ -22726,7 +22727,7 @@
         <v>0.20615287028227219</v>
       </c>
       <c r="AI63" s="0">
-        <v>0.050673963717442302</v>
+        <v>0.050673963717442303</v>
       </c>
       <c r="AJ63" s="0">
         <v>0</v>
@@ -22834,7 +22835,7 @@
         <v>0.0645838378945673</v>
       </c>
       <c r="BS63" s="0">
-        <v>0.0040389353366452867</v>
+        <v>0.0040389353366452868</v>
       </c>
       <c r="BT63" s="0">
         <v>0</v>
@@ -23031,7 +23032,7 @@
         <v>0.23070331553622023</v>
       </c>
       <c r="P64" s="0">
-        <v>0.23886708752772542</v>
+        <v>0.23886708752772543</v>
       </c>
       <c r="Q64" s="0">
         <v>0.36008230452674861</v>
@@ -23124,7 +23125,7 @@
         <v>0</v>
       </c>
       <c r="AU64" s="0">
-        <v>0.037091988130563767</v>
+        <v>0.037091988130563768</v>
       </c>
       <c r="AV64" s="0">
         <v>0.014904240256352921</v>
@@ -23354,7 +23355,7 @@
         <v>0.17979595250041797</v>
       </c>
       <c r="C65" s="0">
-        <v>0.12667550449256137</v>
+        <v>0.12667550449256138</v>
       </c>
       <c r="D65" s="0">
         <v>0.25680955112968862</v>
@@ -23390,7 +23391,7 @@
         <v>0.19730010384215974</v>
       </c>
       <c r="O65" s="0">
-        <v>0.20433722233208076</v>
+        <v>0.20433722233208077</v>
       </c>
       <c r="P65" s="0">
         <v>0.23317977591992245</v>
@@ -23752,7 +23753,7 @@
         <v>0.218068535825545</v>
       </c>
       <c r="O66" s="0">
-        <v>0.098872849515522956</v>
+        <v>0.098872849515522957</v>
       </c>
       <c r="P66" s="0">
         <v>0.24455439913552843</v>
@@ -23905,7 +23906,7 @@
         <v>0</v>
       </c>
       <c r="BN66" s="0">
-        <v>0.031046258925799416</v>
+        <v>0.031046258925799417</v>
       </c>
       <c r="BO66" s="0">
         <v>0.033772374197906088</v>
@@ -23917,7 +23918,7 @@
         <v>0</v>
       </c>
       <c r="BR66" s="0">
-        <v>0.024218939210462562</v>
+        <v>0.024218939210462563</v>
       </c>
       <c r="BS66" s="0">
         <v>0.0040389353366452564</v>
@@ -24476,7 +24477,7 @@
         <v>0.249221183800621</v>
       </c>
       <c r="O68" s="0">
-        <v>0.046140663107243698</v>
+        <v>0.046140663107243699</v>
       </c>
       <c r="P68" s="0">
         <v>0.11374623215605889</v>
@@ -24572,7 +24573,7 @@
         <v>0</v>
       </c>
       <c r="AU68" s="0">
-        <v>0.030909990108802909</v>
+        <v>0.03090999010880291</v>
       </c>
       <c r="AV68" s="0">
         <v>0</v>
@@ -24814,7 +24815,7 @@
         <v>0.063125878740926067</v>
       </c>
       <c r="G69" s="0">
-        <v>0.1335470085470094</v>
+        <v>0.13354700854700941</v>
       </c>
       <c r="H69" s="0">
         <v>0.07064284993440352</v>
@@ -24838,7 +24839,7 @@
         <v>0.062305295950156173</v>
       </c>
       <c r="O69" s="0">
-        <v>0.079098279612418942</v>
+        <v>0.079098279612418943</v>
       </c>
       <c r="P69" s="0">
         <v>0.10237160894045452</v>
@@ -24991,7 +24992,7 @@
         <v>0</v>
       </c>
       <c r="BN69" s="0">
-        <v>0.031046258925799645</v>
+        <v>0.031046258925799646</v>
       </c>
       <c r="BO69" s="0">
         <v>0</v>
@@ -25894,7 +25895,7 @@
         <v>0.035516214517935393</v>
       </c>
       <c r="E72" s="0">
-        <v>0.056069526212503037</v>
+        <v>0.056069526212503038</v>
       </c>
       <c r="F72" s="0">
         <v>0.04017101374422509</v>
@@ -25915,7 +25916,7 @@
         <v>0.038008361839604397</v>
       </c>
       <c r="L72" s="0">
-        <v>0.017758835020422511</v>
+        <v>0.017758835020422512</v>
       </c>
       <c r="M72" s="0">
         <v>0.041580041580041235</v>
@@ -26508,7 +26509,7 @@
         <v>0.052709255745309214</v>
       </c>
       <c r="CK73" s="0">
-        <v>0.0056761742585497744</v>
+        <v>0.0056761742585497745</v>
       </c>
       <c r="CL73" s="0">
         <v>0</v>
@@ -26989,7 +26990,7 @@
         <v>0.013354700854700941</v>
       </c>
       <c r="H75" s="0">
-        <v>0.04036734281965916</v>
+        <v>0.040367342819659161</v>
       </c>
       <c r="I75" s="0">
         <v>0.016611295681063228</v>
@@ -27229,7 +27230,7 @@
         <v>0</v>
       </c>
       <c r="CJ75" s="0">
-        <v>0.042167404596247376</v>
+        <v>0.042167404596247377</v>
       </c>
       <c r="CK75" s="0">
         <v>0</v>
@@ -28419,7 +28420,7 @@
         <v>0.0040252787505534425</v>
       </c>
       <c r="B79" s="0">
-        <v>0.020906506104699608</v>
+        <v>0.020906506104699609</v>
       </c>
       <c r="C79" s="0">
         <v>0.002945941964943266</v>
@@ -28449,7 +28450,7 @@
         <v>0</v>
       </c>
       <c r="L79" s="0">
-        <v>0.017758835020422511</v>
+        <v>0.017758835020422512</v>
       </c>
       <c r="M79" s="0">
         <v>0</v>
